--- a/NBFC-MF/Borrowers/Ronel_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Ronel_Weekly.xlsx
@@ -1736,31 +1736,33 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="19"/>
-      <c r="B11" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A11" s="19">
+        <v>46283</v>
+      </c>
+      <c r="B11" s="23">
+        <f t="shared" si="3"/>
+        <v>10</v>
       </c>
       <c r="C11" s="20"/>
-      <c r="D11" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E11" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F11" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G11" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H11" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D11" s="21">
+        <f t="shared" si="0"/>
+        <v>2100</v>
+      </c>
+      <c r="E11" s="21">
+        <f t="shared" si="1"/>
+        <v>308.39488898078486</v>
+      </c>
+      <c r="F11" s="21">
+        <f t="shared" si="4"/>
+        <v>1791.6051110192152</v>
+      </c>
+      <c r="G11" s="21">
+        <f t="shared" si="5"/>
+        <v>13588.487859238874</v>
+      </c>
+      <c r="H11" s="21">
+        <f t="shared" si="2"/>
+        <v>16411.512140761126</v>
       </c>
       <c r="J11" s="14"/>
     </row>
@@ -1796,7 +1798,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1831,7 +1833,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>16800</v>
+        <v>14700</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1866,7 +1868,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>15380.092970258089</v>
+        <v>13588.487859238874</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1901,7 +1903,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>14619.907029741911</v>
+        <v>16411.512140761126</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Ronel_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Ronel_Weekly.xlsx
@@ -1767,38 +1767,40 @@
       <c r="J11" s="14"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="22" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A12" s="2">
+        <v>46290</v>
+      </c>
+      <c r="B12" s="22">
+        <f t="shared" si="3"/>
+        <v>11</v>
       </c>
       <c r="C12" s="3"/>
-      <c r="D12" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E12" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F12" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G12" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H12" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D12" s="1">
+        <f t="shared" si="0"/>
+        <v>2100</v>
+      </c>
+      <c r="E12" s="1">
+        <f t="shared" si="1"/>
+        <v>272.4704078753299</v>
+      </c>
+      <c r="F12" s="1">
+        <f t="shared" si="4"/>
+        <v>1827.5295921246702</v>
+      </c>
+      <c r="G12" s="1">
+        <f t="shared" si="5"/>
+        <v>11760.958267114203</v>
+      </c>
+      <c r="H12" s="1">
+        <f t="shared" si="2"/>
+        <v>18239.041732885795</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1833,7 +1835,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>14700</v>
+        <v>12600</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1868,7 +1870,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>13588.487859238874</v>
+        <v>11760.958267114203</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1903,7 +1905,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>16411.512140761126</v>
+        <v>18239.041732885795</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Ronel_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Ronel_Weekly.xlsx
@@ -1800,77 +1800,81 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="19"/>
-      <c r="B13" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A13" s="19">
+        <v>46297</v>
+      </c>
+      <c r="B13" s="23">
+        <f t="shared" si="3"/>
+        <v>12</v>
       </c>
       <c r="C13" s="20"/>
-      <c r="D13" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E13" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F13" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G13" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H13" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D13" s="21">
+        <f t="shared" si="0"/>
+        <v>2100</v>
+      </c>
+      <c r="E13" s="21">
+        <f t="shared" si="1"/>
+        <v>235.82558480681701</v>
+      </c>
+      <c r="F13" s="21">
+        <f t="shared" si="4"/>
+        <v>1864.174415193183</v>
+      </c>
+      <c r="G13" s="21">
+        <f t="shared" si="5"/>
+        <v>9896.78385192102</v>
+      </c>
+      <c r="H13" s="21">
+        <f t="shared" si="2"/>
+        <v>20103.21614807898</v>
       </c>
       <c r="J13" s="24" t="s">
         <v>22</v>
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>12600</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="22" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A14" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B14" s="22">
+        <f t="shared" si="3"/>
+        <v>13</v>
       </c>
       <c r="C14" s="3"/>
-      <c r="D14" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E14" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F14" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G14" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H14" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D14" s="1">
+        <f t="shared" si="0"/>
+        <v>2100</v>
+      </c>
+      <c r="E14" s="1">
+        <f t="shared" si="1"/>
+        <v>198.44597579365549</v>
+      </c>
+      <c r="F14" s="1">
+        <f t="shared" si="4"/>
+        <v>1901.5540242063446</v>
+      </c>
+      <c r="G14" s="1">
+        <f t="shared" si="5"/>
+        <v>7995.2298277146756</v>
+      </c>
+      <c r="H14" s="1">
+        <f t="shared" si="2"/>
+        <v>22004.770172285323</v>
       </c>
       <c r="J14" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>11760.958267114203</v>
+        <v>7995.2298277146756</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1905,7 +1909,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>18239.041732885795</v>
+        <v>22004.770172285323</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
